--- a/data/simulations/xa_fixed_v1/SIM_XA_FIXED_seed_20260809/competition_xlsx/企业数据/SIM_XA_FIXED19.xlsx
+++ b/data/simulations/xa_fixed_v1/SIM_XA_FIXED_seed_20260809/competition_xlsx/企业数据/SIM_XA_FIXED19.xlsx
@@ -472,7 +472,7 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>2026-08-09T17:31:57+08:00</t>
+          <t>2026-08-09T17:48:53+08:00</t>
         </is>
       </c>
     </row>
@@ -484,7 +484,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>181W</t>
+          <t>194W</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -1617,7 +1617,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="B2:L4"/>
+  <dimension ref="B2:L6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24" customWidth="1" min="2" max="2"/>
@@ -1700,7 +1700,7 @@
     <row r="4">
       <c r="B4" t="inlineStr">
         <is>
-          <t>SIM_XA_FIXED-2-0087</t>
+          <t>SIM_XA_FIXED-2-0036</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -1714,41 +1714,151 @@
         </is>
       </c>
       <c r="E4" t="n">
+        <v>4</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>106W</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>已交</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>第2年</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>5季</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>1季</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L4" t="inlineStr">
+        <is>
+          <t>第3年3季</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>SIM_XA_FIXED-4-0019</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>本地</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>1</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>30W</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>已交</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>第4年</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>4季</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>0季</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L5" t="inlineStr">
+        <is>
+          <t>第4年3季</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>SIM_XA_FIXED-4-0043</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>本地</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
         <v>2</v>
       </c>
-      <c r="F4" t="inlineStr">
-        <is>
-          <t>55W</t>
-        </is>
-      </c>
-      <c r="G4" t="inlineStr">
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>74W</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
         <is>
           <t>已交</t>
         </is>
       </c>
-      <c r="H4" t="inlineStr">
-        <is>
-          <t>第2年</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>第4年</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
         <is>
           <t>4季</t>
         </is>
       </c>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>2季</t>
-        </is>
-      </c>
-      <c r="K4" t="inlineStr">
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>0季</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="L4" t="inlineStr">
-        <is>
-          <t>第2年4季</t>
+      <c r="L6" t="inlineStr">
+        <is>
+          <t>第5年1季</t>
         </is>
       </c>
     </row>
@@ -1766,7 +1876,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="B2:G50"/>
+  <dimension ref="B2:G55"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="2" max="2"/>
@@ -2086,10 +2196,10 @@
         </is>
       </c>
       <c r="D14" t="n">
-        <v>-4</v>
+        <v>-12</v>
       </c>
       <c r="E14" t="n">
-        <v>488</v>
+        <v>480</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2098,7 +2208,7 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>advertising_expense | {"advertising_key": "本地:P1", "opportunities": 0}</t>
+          <t>advertising_expense | {"advertising_key": "本地:P1", "opportunities": 1}</t>
         </is>
       </c>
     </row>
@@ -2115,7 +2225,7 @@
         <v>-14</v>
       </c>
       <c r="E15" t="n">
-        <v>474</v>
+        <v>466</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2134,14 +2244,14 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Emergency_Buy_Material</t>
+          <t>Auction_Win</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>-24</v>
+        <v>-10</v>
       </c>
       <c r="E16" t="n">
-        <v>450</v>
+        <v>456</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2150,7 +2260,7 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>emergency_material_purchase | {"cost_wan": 24.0, "material_id": "R1", "quantity": 2.0}</t>
+          <t>auction_bid_fee | {"order_id": "SIM_XA_FIXED-2-0165"}</t>
         </is>
       </c>
     </row>
@@ -2160,14 +2270,14 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Product_Produce</t>
+          <t>Pay_Overhaul</t>
         </is>
       </c>
       <c r="D17" t="n">
-        <v>-16</v>
+        <v>-14</v>
       </c>
       <c r="E17" t="n">
-        <v>434</v>
+        <v>442</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2176,7 +2286,7 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>production_started | {"job": {"inventory_cost_wan": 40.0, "job_id": "JOB-379c9790bc", "line_id": "L-c85d36f15f", "product_id": "P1", "quantity": 2.0, "remaining_quarters": 0}}</t>
+          <t>management_fee_expense</t>
         </is>
       </c>
     </row>
@@ -2193,11 +2303,11 @@
         <v>-14</v>
       </c>
       <c r="E18" t="n">
-        <v>420</v>
+        <v>428</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>第2年2季</t>
+          <t>第2年3季</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
@@ -2219,11 +2329,11 @@
         <v>-14</v>
       </c>
       <c r="E19" t="n">
-        <v>406</v>
+        <v>414</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>第2年3季</t>
+          <t>第2年4季</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
@@ -2238,14 +2348,14 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Sell_Product</t>
+          <t>Pay_Maintenance</t>
         </is>
       </c>
       <c r="D20" t="n">
-        <v>0</v>
+        <v>-15</v>
       </c>
       <c r="E20" t="n">
-        <v>406</v>
+        <v>399</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2254,7 +2364,7 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>order_delivered | {"cost_of_goods_sold_wan": 40.0, "order_id": "SIM_XA_FIXED-2-0087", "receivable_term_quarters": 2, "revenue_wan": 55.0}</t>
+          <t>maintenance_expense | {"line_id": "L-c85d36f15f"}</t>
         </is>
       </c>
     </row>
@@ -2264,14 +2374,14 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Emergency_Buy_Material</t>
+          <t>Depreciation</t>
         </is>
       </c>
       <c r="D21" t="n">
-        <v>-24</v>
+        <v>0</v>
       </c>
       <c r="E21" t="n">
-        <v>382</v>
+        <v>399</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2280,7 +2390,7 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>emergency_material_purchase | {"cost_wan": 24.0, "material_id": "R1", "quantity": 2.0}</t>
+          <t>depreciation | {"amount_wan": 7.2, "asset_id": "F-c85d36f15f", "asset_type": "factory"}</t>
         </is>
       </c>
     </row>
@@ -2290,14 +2400,14 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Product_Produce</t>
+          <t>Depreciation</t>
         </is>
       </c>
       <c r="D22" t="n">
-        <v>-16</v>
+        <v>0</v>
       </c>
       <c r="E22" t="n">
-        <v>366</v>
+        <v>399</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2306,7 +2416,7 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>production_started | {"job": {"inventory_cost_wan": 40.0, "job_id": "JOB-4143b47002", "line_id": "L-c85d36f15f", "product_id": "P1", "quantity": 2.0, "remaining_quarters": 0}}</t>
+          <t>depreciation | {"amount_wan": 8.0, "asset_id": "L-c85d36f15f", "asset_type": "production_line"}</t>
         </is>
       </c>
     </row>
@@ -2316,23 +2426,23 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Pay_Overhaul</t>
+          <t>Emergency_Buy_Material</t>
         </is>
       </c>
       <c r="D23" t="n">
-        <v>-14</v>
+        <v>-48</v>
       </c>
       <c r="E23" t="n">
-        <v>352</v>
+        <v>351</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>第2年4季</t>
+          <t>第3年1季</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>management_fee_expense</t>
+          <t>emergency_material_purchase | {"cost_wan": 48.0, "material_id": "R1", "quantity": 4.0}</t>
         </is>
       </c>
     </row>
@@ -2342,23 +2452,23 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Pay_Maintenance</t>
+          <t>Product_Produce</t>
         </is>
       </c>
       <c r="D24" t="n">
-        <v>-15</v>
+        <v>-32</v>
       </c>
       <c r="E24" t="n">
-        <v>337</v>
+        <v>319</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>第2年4季</t>
+          <t>第3年1季</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>maintenance_expense | {"line_id": "L-c85d36f15f"}</t>
+          <t>production_started | {"job": {"inventory_cost_wan": 80.0, "job_id": "JOB-5e62a8f3d7", "line_id": "L-c85d36f15f", "product_id": "P1", "quantity": 4.0, "remaining_quarters": 0}}</t>
         </is>
       </c>
     </row>
@@ -2368,23 +2478,23 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Depreciation</t>
+          <t>Pay_AD</t>
         </is>
       </c>
       <c r="D25" t="n">
-        <v>0</v>
+        <v>-12</v>
       </c>
       <c r="E25" t="n">
-        <v>337</v>
+        <v>307</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>第2年4季</t>
+          <t>第3年1季</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>depreciation | {"amount_wan": 7.2, "asset_id": "F-c85d36f15f", "asset_type": "factory"}</t>
+          <t>advertising_expense | {"advertising_key": "本地:P1", "opportunities": 1}</t>
         </is>
       </c>
     </row>
@@ -2394,23 +2504,23 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Depreciation</t>
+          <t>Pay_Overhaul</t>
         </is>
       </c>
       <c r="D26" t="n">
-        <v>0</v>
+        <v>-14</v>
       </c>
       <c r="E26" t="n">
-        <v>337</v>
+        <v>293</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>第2年4季</t>
+          <t>第3年1季</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>depreciation | {"amount_wan": 8.0, "asset_id": "L-c85d36f15f", "asset_type": "production_line"}</t>
+          <t>management_fee_expense</t>
         </is>
       </c>
     </row>
@@ -2420,23 +2530,23 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Pay_AD</t>
+          <t>Pay_Overhaul</t>
         </is>
       </c>
       <c r="D27" t="n">
-        <v>-4</v>
+        <v>-14</v>
       </c>
       <c r="E27" t="n">
-        <v>333</v>
+        <v>279</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>第3年1季</t>
+          <t>第3年2季</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>advertising_expense | {"advertising_key": "本地:P1", "opportunities": 0}</t>
+          <t>management_fee_expense</t>
         </is>
       </c>
     </row>
@@ -2446,23 +2556,23 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Pay_Overhaul</t>
+          <t>Sell_Product</t>
         </is>
       </c>
       <c r="D28" t="n">
-        <v>-14</v>
+        <v>0</v>
       </c>
       <c r="E28" t="n">
-        <v>319</v>
+        <v>279</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>第3年1季</t>
+          <t>第3年3季</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>management_fee_expense</t>
+          <t>order_delivered | {"cost_of_goods_sold_wan": 80.0, "order_id": "SIM_XA_FIXED-2-0036", "receivable_term_quarters": 1, "revenue_wan": 106.0}</t>
         </is>
       </c>
     </row>
@@ -2472,23 +2582,23 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Update_Receivable</t>
+          <t>Emergency_Buy_Material</t>
         </is>
       </c>
       <c r="D29" t="n">
-        <v>55</v>
+        <v>-48</v>
       </c>
       <c r="E29" t="n">
-        <v>374</v>
+        <v>231</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>第3年1季</t>
+          <t>第3年3季</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>receivable_collected | {"receivable_id": "AR-8d530cbe51"}</t>
+          <t>emergency_material_purchase | {"cost_wan": 48.0, "material_id": "R1", "quantity": 4.0}</t>
         </is>
       </c>
     </row>
@@ -2498,23 +2608,23 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Pay_Overhaul</t>
+          <t>Product_Produce</t>
         </is>
       </c>
       <c r="D30" t="n">
-        <v>-14</v>
+        <v>-32</v>
       </c>
       <c r="E30" t="n">
-        <v>360</v>
+        <v>199</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>第3年2季</t>
+          <t>第3年3季</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>management_fee_expense</t>
+          <t>production_started | {"job": {"inventory_cost_wan": 80.0, "job_id": "JOB-502ee96bb2", "line_id": "L-c85d36f15f", "product_id": "P1", "quantity": 4.0, "remaining_quarters": 0}}</t>
         </is>
       </c>
     </row>
@@ -2531,7 +2641,7 @@
         <v>-14</v>
       </c>
       <c r="E31" t="n">
-        <v>346</v>
+        <v>185</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -2550,23 +2660,23 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Pay_Overhaul</t>
+          <t>Update_Receivable</t>
         </is>
       </c>
       <c r="D32" t="n">
-        <v>-14</v>
+        <v>106</v>
       </c>
       <c r="E32" t="n">
-        <v>332</v>
+        <v>291</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>第3年4季</t>
+          <t>第3年3季</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>management_fee_expense</t>
+          <t>receivable_collected | {"receivable_id": "AR-977535d8c5"}</t>
         </is>
       </c>
     </row>
@@ -2576,14 +2686,14 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Pay_Maintenance</t>
+          <t>Pay_Overhaul</t>
         </is>
       </c>
       <c r="D33" t="n">
-        <v>-15</v>
+        <v>-14</v>
       </c>
       <c r="E33" t="n">
-        <v>317</v>
+        <v>277</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -2592,7 +2702,7 @@
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>maintenance_expense | {"line_id": "L-c85d36f15f"}</t>
+          <t>management_fee_expense</t>
         </is>
       </c>
     </row>
@@ -2602,14 +2712,14 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Depreciation</t>
+          <t>Pay_Maintenance</t>
         </is>
       </c>
       <c r="D34" t="n">
-        <v>0</v>
+        <v>-15</v>
       </c>
       <c r="E34" t="n">
-        <v>317</v>
+        <v>262</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -2618,7 +2728,7 @@
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>depreciation | {"amount_wan": 7.2, "asset_id": "F-c85d36f15f", "asset_type": "factory"}</t>
+          <t>maintenance_expense | {"line_id": "L-c85d36f15f"}</t>
         </is>
       </c>
     </row>
@@ -2635,7 +2745,7 @@
         <v>0</v>
       </c>
       <c r="E35" t="n">
-        <v>317</v>
+        <v>262</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -2644,7 +2754,7 @@
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>depreciation | {"amount_wan": 8.0, "asset_id": "L-c85d36f15f", "asset_type": "production_line"}</t>
+          <t>depreciation | {"amount_wan": 7.2, "asset_id": "F-c85d36f15f", "asset_type": "factory"}</t>
         </is>
       </c>
     </row>
@@ -2654,23 +2764,23 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Pay_AD</t>
+          <t>Depreciation</t>
         </is>
       </c>
       <c r="D36" t="n">
-        <v>-4</v>
+        <v>0</v>
       </c>
       <c r="E36" t="n">
-        <v>313</v>
+        <v>262</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>第4年1季</t>
+          <t>第3年4季</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>advertising_expense | {"advertising_key": "本地:P1", "opportunities": 1}</t>
+          <t>depreciation | {"amount_wan": 8.0, "asset_id": "L-c85d36f15f", "asset_type": "production_line"}</t>
         </is>
       </c>
     </row>
@@ -2680,14 +2790,14 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Pay_Overhaul</t>
+          <t>Pay_AD</t>
         </is>
       </c>
       <c r="D37" t="n">
-        <v>-14</v>
+        <v>-12</v>
       </c>
       <c r="E37" t="n">
-        <v>299</v>
+        <v>250</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -2696,7 +2806,7 @@
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>management_fee_expense</t>
+          <t>advertising_expense | {"advertising_key": "本地:P1", "opportunities": 2}</t>
         </is>
       </c>
     </row>
@@ -2713,11 +2823,11 @@
         <v>-14</v>
       </c>
       <c r="E38" t="n">
-        <v>285</v>
+        <v>236</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>第4年2季</t>
+          <t>第4年1季</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
@@ -2739,11 +2849,11 @@
         <v>-14</v>
       </c>
       <c r="E39" t="n">
-        <v>271</v>
+        <v>222</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>第4年3季</t>
+          <t>第4年2季</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
@@ -2758,23 +2868,23 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Pay_Overhaul</t>
+          <t>Sell_Product</t>
         </is>
       </c>
       <c r="D40" t="n">
-        <v>-14</v>
+        <v>30</v>
       </c>
       <c r="E40" t="n">
-        <v>257</v>
+        <v>252</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>第4年4季</t>
+          <t>第4年3季</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>management_fee_expense</t>
+          <t>order_delivered | {"cost_of_goods_sold_wan": 20.0, "order_id": "SIM_XA_FIXED-4-0019", "receivable_term_quarters": 0, "revenue_wan": 30.0}</t>
         </is>
       </c>
     </row>
@@ -2784,23 +2894,23 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Pay_Maintenance</t>
+          <t>Pay_Overhaul</t>
         </is>
       </c>
       <c r="D41" t="n">
-        <v>-15</v>
+        <v>-14</v>
       </c>
       <c r="E41" t="n">
-        <v>242</v>
+        <v>238</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>第4年4季</t>
+          <t>第4年3季</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>maintenance_expense | {"line_id": "L-c85d36f15f"}</t>
+          <t>management_fee_expense</t>
         </is>
       </c>
     </row>
@@ -2810,14 +2920,14 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Depreciation</t>
+          <t>Pay_Overhaul</t>
         </is>
       </c>
       <c r="D42" t="n">
-        <v>0</v>
+        <v>-14</v>
       </c>
       <c r="E42" t="n">
-        <v>242</v>
+        <v>224</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -2826,7 +2936,7 @@
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>depreciation | {"amount_wan": 7.2, "asset_id": "F-c85d36f15f", "asset_type": "factory"}</t>
+          <t>management_fee_expense</t>
         </is>
       </c>
     </row>
@@ -2836,14 +2946,14 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Depreciation</t>
+          <t>Pay_Maintenance</t>
         </is>
       </c>
       <c r="D43" t="n">
-        <v>0</v>
+        <v>-15</v>
       </c>
       <c r="E43" t="n">
-        <v>242</v>
+        <v>209</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -2852,7 +2962,7 @@
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>depreciation | {"amount_wan": 8.0, "asset_id": "L-c85d36f15f", "asset_type": "production_line"}</t>
+          <t>maintenance_expense | {"line_id": "L-c85d36f15f"}</t>
         </is>
       </c>
     </row>
@@ -2862,23 +2972,23 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Pay_AD</t>
+          <t>Depreciation</t>
         </is>
       </c>
       <c r="D44" t="n">
-        <v>-4</v>
+        <v>0</v>
       </c>
       <c r="E44" t="n">
-        <v>238</v>
+        <v>209</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>第5年1季</t>
+          <t>第4年4季</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>advertising_expense | {"advertising_key": "本地:P1", "opportunities": 1}</t>
+          <t>depreciation | {"amount_wan": 7.2, "asset_id": "F-c85d36f15f", "asset_type": "factory"}</t>
         </is>
       </c>
     </row>
@@ -2888,23 +2998,23 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Pay_Overhaul</t>
+          <t>Depreciation</t>
         </is>
       </c>
       <c r="D45" t="n">
-        <v>-14</v>
+        <v>0</v>
       </c>
       <c r="E45" t="n">
-        <v>224</v>
+        <v>209</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>第5年1季</t>
+          <t>第4年4季</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>management_fee_expense</t>
+          <t>depreciation | {"amount_wan": 8.0, "asset_id": "L-c85d36f15f", "asset_type": "production_line"}</t>
         </is>
       </c>
     </row>
@@ -2914,23 +3024,23 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Pay_Overhaul</t>
+          <t>Sell_Product</t>
         </is>
       </c>
       <c r="D46" t="n">
-        <v>-14</v>
+        <v>74</v>
       </c>
       <c r="E46" t="n">
-        <v>210</v>
+        <v>283</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>第5年2季</t>
+          <t>第5年1季</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>management_fee_expense</t>
+          <t>order_delivered | {"cost_of_goods_sold_wan": 40.0, "order_id": "SIM_XA_FIXED-4-0043", "receivable_term_quarters": 0, "revenue_wan": 74.0}</t>
         </is>
       </c>
     </row>
@@ -2940,23 +3050,23 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Pay_Overhaul</t>
+          <t>Emergency_Buy_Material</t>
         </is>
       </c>
       <c r="D47" t="n">
-        <v>-14</v>
+        <v>-12</v>
       </c>
       <c r="E47" t="n">
-        <v>196</v>
+        <v>271</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>第5年3季</t>
+          <t>第5年1季</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>management_fee_expense</t>
+          <t>emergency_material_purchase | {"cost_wan": 12.0, "material_id": "R1", "quantity": 1.0}</t>
         </is>
       </c>
     </row>
@@ -2966,23 +3076,23 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Pay_Maintenance</t>
+          <t>Product_Produce</t>
         </is>
       </c>
       <c r="D48" t="n">
-        <v>-15</v>
+        <v>-8</v>
       </c>
       <c r="E48" t="n">
-        <v>181</v>
+        <v>263</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>第5年4季</t>
+          <t>第5年1季</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>maintenance_expense | {"line_id": "L-c85d36f15f"}</t>
+          <t>production_started | {"job": {"inventory_cost_wan": 20.0, "job_id": "JOB-f04aed8368", "line_id": "L-c85d36f15f", "product_id": "P1", "quantity": 1.0, "remaining_quarters": 0}}</t>
         </is>
       </c>
     </row>
@@ -2992,23 +3102,23 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Depreciation</t>
+          <t>Pay_AD</t>
         </is>
       </c>
       <c r="D49" t="n">
-        <v>0</v>
+        <v>-12</v>
       </c>
       <c r="E49" t="n">
-        <v>181</v>
+        <v>251</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>第5年4季</t>
+          <t>第5年1季</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>depreciation | {"amount_wan": 7.2, "asset_id": "F-c85d36f15f", "asset_type": "factory"}</t>
+          <t>advertising_expense | {"advertising_key": "本地:P1", "opportunities": 2}</t>
         </is>
       </c>
     </row>
@@ -3018,21 +3128,151 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
+          <t>Pay_Overhaul</t>
+        </is>
+      </c>
+      <c r="D50" t="n">
+        <v>-14</v>
+      </c>
+      <c r="E50" t="n">
+        <v>237</v>
+      </c>
+      <c r="F50" t="inlineStr">
+        <is>
+          <t>第5年1季</t>
+        </is>
+      </c>
+      <c r="G50" t="inlineStr">
+        <is>
+          <t>management_fee_expense</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="B51" t="n">
+        <v>48</v>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>Pay_Overhaul</t>
+        </is>
+      </c>
+      <c r="D51" t="n">
+        <v>-14</v>
+      </c>
+      <c r="E51" t="n">
+        <v>223</v>
+      </c>
+      <c r="F51" t="inlineStr">
+        <is>
+          <t>第5年2季</t>
+        </is>
+      </c>
+      <c r="G51" t="inlineStr">
+        <is>
+          <t>management_fee_expense</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="B52" t="n">
+        <v>49</v>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>Pay_Overhaul</t>
+        </is>
+      </c>
+      <c r="D52" t="n">
+        <v>-14</v>
+      </c>
+      <c r="E52" t="n">
+        <v>209</v>
+      </c>
+      <c r="F52" t="inlineStr">
+        <is>
+          <t>第5年3季</t>
+        </is>
+      </c>
+      <c r="G52" t="inlineStr">
+        <is>
+          <t>management_fee_expense</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="B53" t="n">
+        <v>50</v>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>Pay_Maintenance</t>
+        </is>
+      </c>
+      <c r="D53" t="n">
+        <v>-15</v>
+      </c>
+      <c r="E53" t="n">
+        <v>194</v>
+      </c>
+      <c r="F53" t="inlineStr">
+        <is>
+          <t>第5年4季</t>
+        </is>
+      </c>
+      <c r="G53" t="inlineStr">
+        <is>
+          <t>maintenance_expense | {"line_id": "L-c85d36f15f"}</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="B54" t="n">
+        <v>51</v>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
           <t>Depreciation</t>
         </is>
       </c>
-      <c r="D50" t="n">
-        <v>0</v>
-      </c>
-      <c r="E50" t="n">
-        <v>181</v>
-      </c>
-      <c r="F50" t="inlineStr">
+      <c r="D54" t="n">
+        <v>0</v>
+      </c>
+      <c r="E54" t="n">
+        <v>194</v>
+      </c>
+      <c r="F54" t="inlineStr">
         <is>
           <t>第5年4季</t>
         </is>
       </c>
-      <c r="G50" t="inlineStr">
+      <c r="G54" t="inlineStr">
+        <is>
+          <t>depreciation | {"amount_wan": 7.2, "asset_id": "F-c85d36f15f", "asset_type": "factory"}</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="B55" t="n">
+        <v>52</v>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>Depreciation</t>
+        </is>
+      </c>
+      <c r="D55" t="n">
+        <v>0</v>
+      </c>
+      <c r="E55" t="n">
+        <v>194</v>
+      </c>
+      <c r="F55" t="inlineStr">
+        <is>
+          <t>第5年4季</t>
+        </is>
+      </c>
+      <c r="G55" t="inlineStr">
         <is>
           <t>depreciation | {"amount_wan": 8.0, "asset_id": "L-c85d36f15f", "asset_type": "production_line"}</t>
         </is>
@@ -3139,16 +3379,16 @@
         <v>0</v>
       </c>
       <c r="E4" t="n">
-        <v>4</v>
+        <v>12</v>
       </c>
       <c r="F4" t="n">
-        <v>4</v>
+        <v>12</v>
       </c>
       <c r="G4" t="n">
-        <v>4</v>
+        <v>12</v>
       </c>
       <c r="H4" t="n">
-        <v>4</v>
+        <v>12</v>
       </c>
     </row>
     <row r="5">
@@ -3364,16 +3604,16 @@
         <v>71</v>
       </c>
       <c r="E13" t="n">
-        <v>75</v>
+        <v>83</v>
       </c>
       <c r="F13" t="n">
-        <v>75</v>
+        <v>83</v>
       </c>
       <c r="G13" t="n">
-        <v>75</v>
+        <v>83</v>
       </c>
       <c r="H13" t="n">
-        <v>61</v>
+        <v>69</v>
       </c>
     </row>
     <row r="15">
@@ -3426,16 +3666,16 @@
         <v>0</v>
       </c>
       <c r="E16" t="n">
-        <v>55</v>
+        <v>0</v>
       </c>
       <c r="F16" t="n">
-        <v>0</v>
+        <v>106</v>
       </c>
       <c r="G16" t="n">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="H16" t="n">
-        <v>0</v>
+        <v>74</v>
       </c>
     </row>
     <row r="17">
@@ -3451,16 +3691,16 @@
         <v>0</v>
       </c>
       <c r="E17" t="n">
+        <v>0</v>
+      </c>
+      <c r="F17" t="n">
+        <v>80</v>
+      </c>
+      <c r="G17" t="n">
+        <v>20</v>
+      </c>
+      <c r="H17" t="n">
         <v>40</v>
-      </c>
-      <c r="F17" t="n">
-        <v>0</v>
-      </c>
-      <c r="G17" t="n">
-        <v>0</v>
-      </c>
-      <c r="H17" t="n">
-        <v>0</v>
       </c>
     </row>
     <row r="18">
@@ -3476,16 +3716,16 @@
         <v>0</v>
       </c>
       <c r="E18" t="n">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="F18" t="n">
-        <v>0</v>
+        <v>26</v>
       </c>
       <c r="G18" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="H18" t="n">
-        <v>0</v>
+        <v>34</v>
       </c>
     </row>
     <row r="19">
@@ -3501,16 +3741,16 @@
         <v>71</v>
       </c>
       <c r="E19" t="n">
-        <v>75</v>
+        <v>83</v>
       </c>
       <c r="F19" t="n">
-        <v>75</v>
+        <v>83</v>
       </c>
       <c r="G19" t="n">
-        <v>75</v>
+        <v>83</v>
       </c>
       <c r="H19" t="n">
-        <v>61</v>
+        <v>69</v>
       </c>
     </row>
     <row r="20">
@@ -3526,16 +3766,16 @@
         <v>-71</v>
       </c>
       <c r="E20" t="n">
-        <v>-60</v>
+        <v>-83</v>
       </c>
       <c r="F20" t="n">
-        <v>-75</v>
+        <v>-57</v>
       </c>
       <c r="G20" t="n">
-        <v>-75</v>
+        <v>-73</v>
       </c>
       <c r="H20" t="n">
-        <v>-61</v>
+        <v>-35</v>
       </c>
     </row>
     <row r="21">
@@ -3576,16 +3816,16 @@
         <v>-86.2</v>
       </c>
       <c r="E22" t="n">
-        <v>-75.2</v>
+        <v>-98.2</v>
       </c>
       <c r="F22" t="n">
-        <v>-90.2</v>
+        <v>-72.2</v>
       </c>
       <c r="G22" t="n">
-        <v>-90.2</v>
+        <v>-88.2</v>
       </c>
       <c r="H22" t="n">
-        <v>-76.2</v>
+        <v>-50.2</v>
       </c>
     </row>
     <row r="23">
@@ -3626,16 +3866,16 @@
         <v>-86.2</v>
       </c>
       <c r="E24" t="n">
-        <v>-75.2</v>
+        <v>-108.2</v>
       </c>
       <c r="F24" t="n">
-        <v>-90.2</v>
+        <v>-72.2</v>
       </c>
       <c r="G24" t="n">
-        <v>-90.2</v>
+        <v>-88.2</v>
       </c>
       <c r="H24" t="n">
-        <v>-76.2</v>
+        <v>-50.2</v>
       </c>
     </row>
     <row r="25">
@@ -3676,16 +3916,16 @@
         <v>-86.2</v>
       </c>
       <c r="E26" t="n">
-        <v>-75.2</v>
+        <v>-108.2</v>
       </c>
       <c r="F26" t="n">
-        <v>-90.2</v>
+        <v>-72.2</v>
       </c>
       <c r="G26" t="n">
-        <v>-90.2</v>
+        <v>-88.2</v>
       </c>
       <c r="H26" t="n">
-        <v>-76.2</v>
+        <v>-50.2</v>
       </c>
     </row>
     <row r="28">
@@ -3775,16 +4015,16 @@
         <v>492</v>
       </c>
       <c r="E30" t="n">
-        <v>337</v>
+        <v>399</v>
       </c>
       <c r="F30" t="n">
-        <v>317</v>
+        <v>262</v>
       </c>
       <c r="G30" t="n">
-        <v>242</v>
+        <v>209</v>
       </c>
       <c r="H30" t="n">
-        <v>181</v>
+        <v>194</v>
       </c>
     </row>
     <row r="31">
@@ -3800,7 +4040,7 @@
         <v>0</v>
       </c>
       <c r="E31" t="n">
-        <v>55</v>
+        <v>0</v>
       </c>
       <c r="F31" t="n">
         <v>0</v>
@@ -3825,7 +4065,7 @@
         <v>0</v>
       </c>
       <c r="E32" t="n">
-        <v>40</v>
+        <v>0</v>
       </c>
       <c r="F32" t="n">
         <v>0</v>
@@ -3853,10 +4093,10 @@
         <v>0</v>
       </c>
       <c r="F33" t="n">
-        <v>40</v>
+        <v>80</v>
       </c>
       <c r="G33" t="n">
-        <v>40</v>
+        <v>60</v>
       </c>
       <c r="H33" t="n">
         <v>40</v>
@@ -3900,16 +4140,16 @@
         <v>492</v>
       </c>
       <c r="E35" t="n">
-        <v>432</v>
+        <v>399</v>
       </c>
       <c r="F35" t="n">
-        <v>357</v>
+        <v>342</v>
       </c>
       <c r="G35" t="n">
-        <v>282</v>
+        <v>269</v>
       </c>
       <c r="H35" t="n">
-        <v>221</v>
+        <v>234</v>
       </c>
     </row>
     <row r="36">
@@ -4025,16 +4265,16 @@
         <v>588.8</v>
       </c>
       <c r="E40" t="n">
-        <v>513.6</v>
+        <v>480.6</v>
       </c>
       <c r="F40" t="n">
-        <v>423.4</v>
+        <v>408.4</v>
       </c>
       <c r="G40" t="n">
-        <v>333.2</v>
+        <v>320.2</v>
       </c>
       <c r="H40" t="n">
-        <v>257</v>
+        <v>270</v>
       </c>
     </row>
     <row r="41">
@@ -4200,16 +4440,16 @@
         <v>-4.263256414560601e-14</v>
       </c>
       <c r="E47" t="n">
-        <v>-86.20000000000009</v>
+        <v>-86.20000000000003</v>
       </c>
       <c r="F47" t="n">
-        <v>-161.4000000000001</v>
+        <v>-194.4</v>
       </c>
       <c r="G47" t="n">
-        <v>-251.6000000000001</v>
+        <v>-266.6</v>
       </c>
       <c r="H47" t="n">
-        <v>-341.8000000000001</v>
+        <v>-354.8</v>
       </c>
     </row>
     <row r="48">
@@ -4225,16 +4465,16 @@
         <v>-86.2</v>
       </c>
       <c r="E48" t="n">
-        <v>-75.2</v>
+        <v>-108.2</v>
       </c>
       <c r="F48" t="n">
-        <v>-90.2</v>
+        <v>-72.2</v>
       </c>
       <c r="G48" t="n">
-        <v>-90.2</v>
+        <v>-88.2</v>
       </c>
       <c r="H48" t="n">
-        <v>-76.2</v>
+        <v>-50.2</v>
       </c>
     </row>
     <row r="49">
@@ -4250,16 +4490,16 @@
         <v>588.8</v>
       </c>
       <c r="E49" t="n">
-        <v>513.5999999999999</v>
+        <v>480.6</v>
       </c>
       <c r="F49" t="n">
-        <v>423.3999999999999</v>
+        <v>408.4</v>
       </c>
       <c r="G49" t="n">
-        <v>333.1999999999999</v>
+        <v>320.2</v>
       </c>
       <c r="H49" t="n">
-        <v>256.9999999999999</v>
+        <v>270</v>
       </c>
     </row>
     <row r="50">
@@ -4275,16 +4515,16 @@
         <v>588.8</v>
       </c>
       <c r="E50" t="n">
-        <v>513.5999999999999</v>
+        <v>480.6</v>
       </c>
       <c r="F50" t="n">
-        <v>423.3999999999999</v>
+        <v>408.4</v>
       </c>
       <c r="G50" t="n">
-        <v>333.1999999999999</v>
+        <v>320.2</v>
       </c>
       <c r="H50" t="n">
-        <v>256.9999999999999</v>
+        <v>270</v>
       </c>
     </row>
   </sheetData>
@@ -4355,7 +4595,7 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>16</v>
+        <v>48</v>
       </c>
       <c r="D4" t="n">
         <v>0</v>
@@ -4504,7 +4744,7 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>16</v>
+        <v>48</v>
       </c>
       <c r="D12" t="n">
         <v>0</v>
@@ -4653,7 +4893,7 @@
         </is>
       </c>
       <c r="C20" t="n">
-        <v>16</v>
+        <v>48</v>
       </c>
       <c r="D20" t="n">
         <v>0</v>
@@ -4802,7 +5042,7 @@
         </is>
       </c>
       <c r="C28" t="n">
-        <v>16</v>
+        <v>48</v>
       </c>
       <c r="D28" t="n">
         <v>0</v>
@@ -4951,7 +5191,7 @@
         </is>
       </c>
       <c r="C36" t="n">
-        <v>16</v>
+        <v>48</v>
       </c>
       <c r="D36" t="n">
         <v>0</v>
